--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -19,64 +19,85 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="15">
-  <si>
-    <t xml:space="preserve">Name </t>
-  </si>
-  <si>
-    <t>father Name</t>
-  </si>
-  <si>
-    <t>SurName</t>
-  </si>
-  <si>
-    <t>Address</t>
-  </si>
-  <si>
-    <t>Age</t>
-  </si>
-  <si>
-    <t>James</t>
-  </si>
-  <si>
-    <t>Yatusho</t>
-  </si>
-  <si>
-    <t>Yakoho</t>
-  </si>
-  <si>
-    <t>Japan</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jonatan </t>
-  </si>
-  <si>
-    <t>will</t>
-  </si>
-  <si>
-    <t>USA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">William </t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bayers </t>
-  </si>
-  <si>
-    <t>UK</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+  <si>
+    <t>Title</t>
+  </si>
+  <si>
+    <t>AssinedTo</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Company</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Priority</t>
+  </si>
+  <si>
+    <t>Status</t>
+  </si>
+  <si>
+    <t>Test Home</t>
+  </si>
+  <si>
+    <t>Omkar Khopade</t>
+  </si>
+  <si>
+    <t>General Support</t>
+  </si>
+  <si>
+    <t>Accenture</t>
+  </si>
+  <si>
+    <t>Test123</t>
+  </si>
+  <si>
+    <t>This Test Home task and assigned to Omkar Khopade</t>
+  </si>
+  <si>
+    <t>High</t>
+  </si>
+  <si>
+    <t>Enquiring</t>
+  </si>
+  <si>
+    <t>Menu</t>
+  </si>
+  <si>
+    <t>Task</t>
+  </si>
+  <si>
+    <t>Delete</t>
+  </si>
+  <si>
+    <t>yuyuuy</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -99,8 +120,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -381,81 +404,88 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E4"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="8.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="4.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15" customWidth="1"/>
+    <col min="8" max="8" width="48.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.28515625" customWidth="1"/>
+    <col min="10" max="10" width="13.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
+        <v>16</v>
+      </c>
+      <c r="B1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="D1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="E1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
         <v>4</v>
       </c>
+      <c r="H1" t="s">
+        <v>5</v>
+      </c>
+      <c r="I1" t="s">
+        <v>6</v>
+      </c>
+      <c r="J1" t="s">
+        <v>7</v>
+      </c>
+      <c r="K1" t="s">
+        <v>19</v>
+      </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>6</v>
+        <v>17</v>
+      </c>
+      <c r="B2" s="2" t="b">
+        <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D2" t="s">
         <v>8</v>
       </c>
-      <c r="E2">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="D2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B3" t="s">
+      <c r="E2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" t="s">
+      <c r="F2" t="s">
         <v>11</v>
       </c>
-      <c r="E3">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="G2" t="s">
         <v>12</v>
       </c>
-      <c r="B4" t="s">
+      <c r="H2" t="s">
         <v>13</v>
       </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
+      <c r="I2" t="s">
         <v>14</v>
       </c>
-      <c r="E4">
-        <v>35</v>
+      <c r="J2" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/TestData/TestData.xlsx
+++ b/TestData/TestData.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="26">
   <si>
     <t>Title</t>
   </si>
@@ -78,7 +78,25 @@
     <t>Delete</t>
   </si>
   <si>
-    <t>yuyuuy</t>
+    <t>Contact</t>
+  </si>
+  <si>
+    <t>FirstName</t>
+  </si>
+  <si>
+    <t>LastName</t>
+  </si>
+  <si>
+    <t>MiddleName</t>
+  </si>
+  <si>
+    <t>Test Omkar</t>
+  </si>
+  <si>
+    <t>Khopade</t>
+  </si>
+  <si>
+    <t>Maruti</t>
   </si>
 </sst>
 </file>
@@ -404,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:M3"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="10.42578125" bestFit="1" customWidth="1"/>
@@ -415,9 +433,12 @@
     <col min="8" max="8" width="48.42578125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13.28515625" customWidth="1"/>
     <col min="10" max="10" width="13.85546875" customWidth="1"/>
+    <col min="11" max="11" width="11" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>16</v>
       </c>
@@ -449,10 +470,16 @@
         <v>7</v>
       </c>
       <c r="K1" t="s">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="L1" t="s">
+        <v>21</v>
+      </c>
+      <c r="M1" t="s">
+        <v>22</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>17</v>
       </c>
@@ -482,6 +509,23 @@
       </c>
       <c r="J2" t="s">
         <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B3" t="b">
+        <v>1</v>
+      </c>
+      <c r="K3" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M3" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
